--- a/src/results.xlsx
+++ b/src/results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\dashboards\world_cup_dashboard\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720915EF-C001-4690-9464-0F2F3A8E6949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD207A76-3677-48C7-B759-EA08E0F209E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="131">
   <si>
     <t>Match_ID</t>
   </si>
@@ -429,6 +429,9 @@
   </si>
   <si>
     <t>4-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
   </si>
 </sst>
 </file>
@@ -471,7 +474,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -494,11 +497,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -510,6 +524,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1469,7 +1486,9 @@
       <c r="D24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="F24" s="2" t="b">
         <v>0</v>
       </c>
@@ -1492,6 +1511,9 @@
       </c>
       <c r="D25" s="2" t="s">
         <v>50</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="F25" s="2" t="b">
         <v>0</v>

--- a/src/results.xlsx
+++ b/src/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD207A76-3677-48C7-B759-EA08E0F209E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B3F825-AF09-4BF7-A386-87AA3AE57B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
+    <workbookView xWindow="-1530" yWindow="16200" windowWidth="22800" windowHeight="14565" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="134">
   <si>
     <t>Match_ID</t>
   </si>
@@ -432,6 +432,15 @@
   </si>
   <si>
     <t>1-3</t>
+  </si>
+  <si>
+    <t>6-0</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>4-0</t>
   </si>
 </sst>
 </file>
@@ -512,7 +521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -526,9 +535,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -864,18 +877,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB71FD8C-39D1-472E-8243-C376DFC76F71}">
   <dimension ref="A1:H105"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="21.1796875" customWidth="1"/>
-    <col min="4" max="4" width="34.54296875" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="16.1796875" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -888,7 +901,7 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -901,7 +914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -927,7 +940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -953,7 +966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -979,7 +992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1005,7 +1018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1031,7 +1044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1057,7 +1070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1083,7 +1096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1109,7 +1122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1135,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1161,7 +1174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1187,7 +1200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1213,7 +1226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1239,7 +1252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1265,7 +1278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1291,7 +1304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1317,7 +1330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1343,7 +1356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1369,7 +1382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1395,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1421,7 +1434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1447,7 +1460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1473,7 +1486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1499,7 +1512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1525,7 +1538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1538,6 +1551,9 @@
       <c r="D26" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="E26" s="7" t="s">
+        <v>118</v>
+      </c>
       <c r="F26" s="2" t="b">
         <v>0</v>
       </c>
@@ -1548,7 +1564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1561,6 +1577,9 @@
       <c r="D27" s="2" t="s">
         <v>116</v>
       </c>
+      <c r="E27" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="F27" s="2" t="b">
         <v>0</v>
       </c>
@@ -1571,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1584,6 +1603,9 @@
       <c r="D28" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="E28" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="F28" s="2" t="b">
         <v>0</v>
       </c>
@@ -1594,7 +1616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1607,6 +1629,9 @@
       <c r="D29" s="2" t="s">
         <v>112</v>
       </c>
+      <c r="E29" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="F29" s="2" t="b">
         <v>0</v>
       </c>
@@ -1617,7 +1642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1630,6 +1655,9 @@
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="E30" s="7" t="s">
+        <v>113</v>
+      </c>
       <c r="F30" s="2" t="b">
         <v>0</v>
       </c>
@@ -1640,7 +1668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1653,6 +1681,9 @@
       <c r="D31" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E31" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="F31" s="2" t="b">
         <v>0</v>
       </c>
@@ -1663,7 +1694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1676,6 +1707,9 @@
       <c r="D32" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="E32" s="7" t="s">
+        <v>128</v>
+      </c>
       <c r="F32" s="2" t="b">
         <v>0</v>
       </c>
@@ -1686,7 +1720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1699,6 +1733,9 @@
       <c r="D33" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="E33" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="F33" s="2" t="b">
         <v>0</v>
       </c>
@@ -1709,7 +1746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1722,6 +1759,9 @@
       <c r="D34" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="E34" s="7" t="s">
+        <v>124</v>
+      </c>
       <c r="F34" s="2" t="b">
         <v>0</v>
       </c>
@@ -1732,7 +1772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1745,6 +1785,9 @@
       <c r="D35" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="E35" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="F35" s="2" t="b">
         <v>0</v>
       </c>
@@ -1755,7 +1798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1768,6 +1811,9 @@
       <c r="D36" s="2" t="s">
         <v>115</v>
       </c>
+      <c r="E36" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="F36" s="2" t="b">
         <v>0</v>
       </c>
@@ -1778,7 +1824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1791,6 +1837,9 @@
       <c r="D37" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="E37" s="7" t="s">
+        <v>132</v>
+      </c>
       <c r="F37" s="2" t="b">
         <v>0</v>
       </c>
@@ -1801,7 +1850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1814,6 +1863,9 @@
       <c r="D38" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="E38" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="F38" s="2" t="b">
         <v>0</v>
       </c>
@@ -1824,7 +1876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1837,6 +1889,9 @@
       <c r="D39" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="E39" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="F39" s="2" t="b">
         <v>0</v>
       </c>
@@ -1847,7 +1902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1870,7 +1925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1893,7 +1948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1916,7 +1971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -1939,7 +1994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -1962,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -1985,7 +2040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2008,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2031,7 +2086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2054,7 +2109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2077,7 +2132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2100,7 +2155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2123,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2146,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2169,7 +2224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2192,7 +2247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2215,7 +2270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2238,7 +2293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2261,7 +2316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2284,7 +2339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2307,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2330,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2353,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2376,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2399,7 +2454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -2422,7 +2477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2445,7 +2500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -2468,7 +2523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2491,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -2514,7 +2569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2537,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2560,7 +2615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2583,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2606,7 +2661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2629,7 +2684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2646,7 +2701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2663,7 +2718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2680,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -2697,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -2714,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -2731,7 +2786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -2748,7 +2803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -2765,7 +2820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -2782,7 +2837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -2799,7 +2854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -2816,7 +2871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -2833,7 +2888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -2850,7 +2905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -2867,7 +2922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -2884,7 +2939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -2901,7 +2956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -2918,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -2933,7 +2988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -2948,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -2963,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -2978,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -2993,7 +3048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -3008,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -3023,7 +3078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -3038,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -3053,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -3068,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -3083,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -3098,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -3113,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -3128,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>104</v>
       </c>

--- a/src/results.xlsx
+++ b/src/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B3F825-AF09-4BF7-A386-87AA3AE57B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47613E0-9023-4310-94BD-FFA15E4F495C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1530" yWindow="16200" windowWidth="22800" windowHeight="14565" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="137">
   <si>
     <t>Match_ID</t>
   </si>
@@ -441,6 +441,15 @@
   </si>
   <si>
     <t>4-0</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>5-0</t>
   </si>
 </sst>
 </file>
@@ -877,18 +886,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB71FD8C-39D1-472E-8243-C376DFC76F71}">
   <dimension ref="A1:H105"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1796875" customWidth="1"/>
+    <col min="4" max="4" width="34.54296875" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -914,7 +923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -940,7 +949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -966,7 +975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -992,7 +1001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1018,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1044,7 +1053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1070,7 +1079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1096,7 +1105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1122,7 +1131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1148,7 +1157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1174,7 +1183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1200,7 +1209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1226,7 +1235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1252,7 +1261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1278,7 +1287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1304,7 +1313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1330,7 +1339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1356,7 +1365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1382,7 +1391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1408,7 +1417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1434,7 +1443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1460,7 +1469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1486,7 +1495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1512,7 +1521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1538,7 +1547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1564,7 +1573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1590,7 +1599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1616,7 +1625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1642,7 +1651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1668,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1694,7 +1703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1720,7 +1729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1746,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1772,7 +1781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1798,7 +1807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1824,7 +1833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1850,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1876,7 +1885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1902,7 +1911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1915,6 +1924,9 @@
       <c r="D40" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="E40" s="7" t="s">
+        <v>122</v>
+      </c>
       <c r="F40" s="2" t="b">
         <v>0</v>
       </c>
@@ -1925,7 +1937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1938,6 +1950,9 @@
       <c r="D41" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E41" s="7" t="s">
+        <v>130</v>
+      </c>
       <c r="F41" s="2" t="b">
         <v>0</v>
       </c>
@@ -1948,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1961,6 +1976,9 @@
       <c r="D42" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="E42" s="7" t="s">
+        <v>113</v>
+      </c>
       <c r="F42" s="2" t="b">
         <v>0</v>
       </c>
@@ -1971,7 +1989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -1984,6 +2002,9 @@
       <c r="D43" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="E43" s="7" t="s">
+        <v>128</v>
+      </c>
       <c r="F43" s="2" t="b">
         <v>0</v>
       </c>
@@ -1994,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2007,6 +2028,9 @@
       <c r="D44" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="E44" s="7" t="s">
+        <v>134</v>
+      </c>
       <c r="F44" s="2" t="b">
         <v>0</v>
       </c>
@@ -2017,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2030,6 +2054,9 @@
       <c r="D45" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="E45" s="7" t="s">
+        <v>135</v>
+      </c>
       <c r="F45" s="2" t="b">
         <v>0</v>
       </c>
@@ -2040,7 +2067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2053,6 +2080,9 @@
       <c r="D46" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="E46" s="7" t="s">
+        <v>136</v>
+      </c>
       <c r="F46" s="2" t="b">
         <v>0</v>
       </c>
@@ -2063,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2076,6 +2106,9 @@
       <c r="D47" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="E47" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="F47" s="2" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2099,6 +2132,9 @@
       <c r="D48" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="E48" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="F48" s="2" t="b">
         <v>0</v>
       </c>
@@ -2109,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2122,6 +2158,9 @@
       <c r="D49" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="E49" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="F49" s="2" t="b">
         <v>0</v>
       </c>
@@ -2132,7 +2171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2145,6 +2184,9 @@
       <c r="D50" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="E50" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="F50" s="2" t="b">
         <v>0</v>
       </c>
@@ -2155,7 +2197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2168,6 +2210,9 @@
       <c r="D51" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="E51" s="7" t="s">
+        <v>126</v>
+      </c>
       <c r="F51" s="2" t="b">
         <v>0</v>
       </c>
@@ -2178,7 +2223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2201,7 +2246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2224,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2247,7 +2292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2270,7 +2315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2293,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2316,7 +2361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2339,7 +2384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2362,7 +2407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2385,7 +2430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2408,7 +2453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2431,7 +2476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2454,7 +2499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -2477,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2500,7 +2545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -2523,7 +2568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2546,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -2569,7 +2614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2592,7 +2637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2615,7 +2660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2638,7 +2683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2661,7 +2706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2684,7 +2729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2701,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2718,7 +2763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2735,7 +2780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -2752,7 +2797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -2769,7 +2814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -2786,7 +2831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -2803,7 +2848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -2820,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -2837,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -2854,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -2871,7 +2916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -2888,7 +2933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -2905,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -2922,7 +2967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -2939,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -2956,7 +3001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -2973,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -2988,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -3003,7 +3048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -3018,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -3033,7 +3078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -3048,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -3063,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -3078,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -3093,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -3108,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -3123,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -3138,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -3153,7 +3198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -3168,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -3183,7 +3228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="2">
         <v>104</v>
       </c>

--- a/src/results.xlsx
+++ b/src/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47613E0-9023-4310-94BD-FFA15E4F495C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87574103-F03A-41B2-A9B7-F9A15B521F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
+    <workbookView xWindow="-1270" yWindow="-17870" windowWidth="16920" windowHeight="10450" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="145">
   <si>
     <t>Match_ID</t>
   </si>
@@ -450,6 +450,30 @@
   </si>
   <si>
     <t>5-0</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>29 June 7:00am</t>
+  </si>
+  <si>
+    <t>30 June 5:00am</t>
+  </si>
+  <si>
+    <t>30 June 8:30am</t>
+  </si>
+  <si>
+    <t>30 June 1:00pm</t>
   </si>
 </sst>
 </file>
@@ -2236,6 +2260,9 @@
       <c r="D52" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="E52" s="7" t="s">
+        <v>129</v>
+      </c>
       <c r="F52" s="2" t="b">
         <v>0</v>
       </c>
@@ -2259,6 +2286,9 @@
       <c r="D53" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="E53" s="7" t="s">
+        <v>137</v>
+      </c>
       <c r="F53" s="2" t="b">
         <v>0</v>
       </c>
@@ -2282,6 +2312,9 @@
       <c r="D54" s="2" t="s">
         <v>112</v>
       </c>
+      <c r="E54" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="F54" s="2" t="b">
         <v>0</v>
       </c>
@@ -2305,6 +2338,9 @@
       <c r="D55" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E55" s="7" t="s">
+        <v>137</v>
+      </c>
       <c r="F55" s="2" t="b">
         <v>0</v>
       </c>
@@ -2328,6 +2364,9 @@
       <c r="D56" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="E56" s="7" t="s">
+        <v>138</v>
+      </c>
       <c r="F56" s="2" t="b">
         <v>0</v>
       </c>
@@ -2351,6 +2390,9 @@
       <c r="D57" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="E57" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="F57" s="2" t="b">
         <v>0</v>
       </c>
@@ -2374,6 +2416,9 @@
       <c r="D58" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="E58" s="7" t="s">
+        <v>130</v>
+      </c>
       <c r="F58" s="2" t="b">
         <v>0</v>
       </c>
@@ -2397,6 +2442,9 @@
       <c r="D59" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="E59" s="7" t="s">
+        <v>118</v>
+      </c>
       <c r="F59" s="2" t="b">
         <v>0</v>
       </c>
@@ -2420,6 +2468,9 @@
       <c r="D60" s="2" t="s">
         <v>114</v>
       </c>
+      <c r="E60" s="7" t="s">
+        <v>134</v>
+      </c>
       <c r="F60" s="2" t="b">
         <v>0</v>
       </c>
@@ -2443,6 +2494,9 @@
       <c r="D61" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="E61" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="F61" s="2" t="b">
         <v>0</v>
       </c>
@@ -2466,6 +2520,9 @@
       <c r="D62" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="E62" s="7" t="s">
+        <v>127</v>
+      </c>
       <c r="F62" s="2" t="b">
         <v>0</v>
       </c>
@@ -2489,6 +2546,9 @@
       <c r="D63" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="E63" s="7" t="s">
+        <v>136</v>
+      </c>
       <c r="F63" s="2" t="b">
         <v>0</v>
       </c>
@@ -2512,6 +2572,9 @@
       <c r="D64" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="E64" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="F64" s="2" t="b">
         <v>0</v>
       </c>
@@ -2535,6 +2598,9 @@
       <c r="D65" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="E65" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="F65" s="2" t="b">
         <v>0</v>
       </c>
@@ -2558,6 +2624,9 @@
       <c r="D66" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="E66" s="7" t="s">
+        <v>139</v>
+      </c>
       <c r="F66" s="2" t="b">
         <v>0</v>
       </c>
@@ -2581,6 +2650,9 @@
       <c r="D67" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="E67" s="7" t="s">
+        <v>118</v>
+      </c>
       <c r="F67" s="2" t="b">
         <v>0</v>
       </c>
@@ -2604,6 +2676,9 @@
       <c r="D68" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="E68" s="7" t="s">
+        <v>138</v>
+      </c>
       <c r="F68" s="2" t="b">
         <v>0</v>
       </c>
@@ -2627,6 +2702,9 @@
       <c r="D69" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="E69" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="F69" s="2" t="b">
         <v>0</v>
       </c>
@@ -2650,6 +2728,9 @@
       <c r="D70" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="E70" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="F70" s="2" t="b">
         <v>0</v>
       </c>
@@ -2673,6 +2754,9 @@
       <c r="D71" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="E71" s="7" t="s">
+        <v>126</v>
+      </c>
       <c r="F71" s="2" t="b">
         <v>0</v>
       </c>
@@ -2696,6 +2780,9 @@
       <c r="D72" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="E72" s="7" t="s">
+        <v>140</v>
+      </c>
       <c r="F72" s="2" t="b">
         <v>0</v>
       </c>
@@ -2719,6 +2806,9 @@
       <c r="D73" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="E73" s="7" t="s">
+        <v>130</v>
+      </c>
       <c r="F73" s="2" t="b">
         <v>0</v>
       </c>
@@ -2733,9 +2823,18 @@
       <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="F74" s="2" t="b">
         <v>0</v>
       </c>
@@ -2750,9 +2849,15 @@
       <c r="A75" s="2">
         <v>74</v>
       </c>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
+      <c r="B75" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F75" s="2" t="b">
         <v>0</v>
       </c>
@@ -2767,9 +2872,15 @@
       <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
+      <c r="B76" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="F76" s="2" t="b">
         <v>0</v>
       </c>
@@ -2784,9 +2895,15 @@
       <c r="A77" s="2">
         <v>76</v>
       </c>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="F77" s="2" t="b">
         <v>0</v>
       </c>

--- a/src/results.xlsx
+++ b/src/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87574103-F03A-41B2-A9B7-F9A15B521F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE17B339-E0BA-4966-B3F7-2A12B4EB74F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1270" yWindow="-17870" windowWidth="16920" windowHeight="10450" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22800" windowHeight="14565" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="147">
   <si>
     <t>Match_ID</t>
   </si>
@@ -474,6 +474,12 @@
   </si>
   <si>
     <t>30 June 1:00pm</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-3</t>
   </si>
 </sst>
 </file>
@@ -910,18 +916,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB71FD8C-39D1-472E-8243-C376DFC76F71}">
   <dimension ref="A1:H105"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="21.1796875" customWidth="1"/>
-    <col min="4" max="4" width="34.54296875" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="16.1796875" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -947,7 +953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -973,7 +979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -999,7 +1005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1025,7 +1031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1051,7 +1057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1077,7 +1083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1103,7 +1109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1129,7 +1135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1155,7 +1161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1181,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1207,7 +1213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1233,7 +1239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1259,7 +1265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1285,7 +1291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1311,7 +1317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1337,7 +1343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1363,7 +1369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1389,7 +1395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1415,7 +1421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1441,7 +1447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1467,7 +1473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1493,7 +1499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1519,7 +1525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1545,7 +1551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1571,7 +1577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1597,7 +1603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1623,7 +1629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1649,7 +1655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1675,7 +1681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1701,7 +1707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1727,7 +1733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1753,7 +1759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1779,7 +1785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1805,7 +1811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1831,7 +1837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1857,7 +1863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1883,7 +1889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1909,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1935,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1961,7 +1967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1987,7 +1993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2013,7 +2019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2039,7 +2045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2065,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2091,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2117,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2143,7 +2149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2169,7 +2175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2195,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2221,7 +2227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2247,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2273,7 +2279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2299,7 +2305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2325,7 +2331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2351,7 +2357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2377,7 +2383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2403,7 +2409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2429,7 +2435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2455,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2481,7 +2487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2507,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2533,7 +2539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2559,7 +2565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -2585,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2611,7 +2617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -2637,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2663,7 +2669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -2689,7 +2695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2715,7 +2721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2741,7 +2747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2767,7 +2773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2793,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2819,7 +2825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2845,7 +2851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2858,6 +2864,9 @@
       <c r="D75" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="E75" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="F75" s="2" t="b">
         <v>0</v>
       </c>
@@ -2868,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2881,6 +2890,9 @@
       <c r="D76" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="E76" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="F76" s="2" t="b">
         <v>0</v>
       </c>
@@ -2891,7 +2903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -2904,6 +2916,9 @@
       <c r="D77" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E77" s="7" t="s">
+        <v>146</v>
+      </c>
       <c r="F77" s="2" t="b">
         <v>0</v>
       </c>
@@ -2914,13 +2929,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
+      <c r="C78" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>135</v>
+      </c>
       <c r="F78" s="2" t="b">
         <v>0</v>
       </c>
@@ -2931,13 +2953,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>78</v>
       </c>
       <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
+      <c r="C79" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>128</v>
+      </c>
       <c r="F79" s="2" t="b">
         <v>0</v>
       </c>
@@ -2948,13 +2977,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
+      <c r="C80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>113</v>
+      </c>
       <c r="F80" s="2" t="b">
         <v>0</v>
       </c>
@@ -2965,13 +3001,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>80</v>
       </c>
       <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
+      <c r="C81" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="F81" s="2" t="b">
         <v>0</v>
       </c>
@@ -2982,13 +3025,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
+      <c r="C82" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>134</v>
+      </c>
       <c r="F82" s="2" t="b">
         <v>0</v>
       </c>
@@ -2999,13 +3049,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
+      <c r="C83" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>113</v>
+      </c>
       <c r="F83" s="2" t="b">
         <v>0</v>
       </c>
@@ -3016,13 +3073,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
+      <c r="C84" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>128</v>
+      </c>
       <c r="F84" s="2" t="b">
         <v>0</v>
       </c>
@@ -3033,13 +3097,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
+      <c r="C85" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="F85" s="2" t="b">
         <v>0</v>
       </c>
@@ -3050,13 +3118,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
+      <c r="C86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="F86" s="2" t="b">
         <v>0</v>
       </c>
@@ -3067,13 +3139,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
+      <c r="C87" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="F87" s="2" t="b">
         <v>0</v>
       </c>
@@ -3084,13 +3160,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>87</v>
       </c>
       <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
+      <c r="C88" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="F88" s="2" t="b">
         <v>0</v>
       </c>
@@ -3101,13 +3181,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>88</v>
       </c>
       <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
+      <c r="C89" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="F89" s="2" t="b">
         <v>0</v>
       </c>
@@ -3118,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -3135,7 +3219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3150,7 +3234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -3165,7 +3249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -3180,7 +3264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -3195,7 +3279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -3210,7 +3294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -3225,7 +3309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -3240,7 +3324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -3255,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -3270,7 +3354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -3285,7 +3369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -3300,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -3315,7 +3399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -3330,7 +3414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -3345,7 +3429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>104</v>
       </c>

--- a/src/results.xlsx
+++ b/src/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE17B339-E0BA-4966-B3F7-2A12B4EB74F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029D1F33-3A01-47F6-9935-F4BAF765E892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="22800" windowHeight="14565" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
+    <workbookView xWindow="-1850" yWindow="16090" windowWidth="22780" windowHeight="14540" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="166">
   <si>
     <t>Match_ID</t>
   </si>
@@ -480,6 +480,63 @@
   </si>
   <si>
     <t>2-3</t>
+  </si>
+  <si>
+    <t>1 July 5:00am</t>
+  </si>
+  <si>
+    <t>1 July 9:00am</t>
+  </si>
+  <si>
+    <t>1 July 1:00pm</t>
+  </si>
+  <si>
+    <t>2 July 4:00am</t>
+  </si>
+  <si>
+    <t>2 July 8:00am</t>
+  </si>
+  <si>
+    <t>2 July 12:00pm</t>
+  </si>
+  <si>
+    <t>3 July 7:00am</t>
+  </si>
+  <si>
+    <t>3 July 11:00am</t>
+  </si>
+  <si>
+    <t>3 July 3:00pm</t>
+  </si>
+  <si>
+    <t>4 July 6:00am</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>4 July 10:00am</t>
+  </si>
+  <si>
+    <t>4 July 1:30am</t>
+  </si>
+  <si>
+    <t>5 July 1:30am</t>
+  </si>
+  <si>
+    <t>7 July 7:00am</t>
+  </si>
+  <si>
+    <t>7 July 12:00pm</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>15 July 7:00am</t>
+  </si>
+  <si>
+    <t>16 July 7:00am</t>
   </si>
 </sst>
 </file>
@@ -916,18 +973,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB71FD8C-39D1-472E-8243-C376DFC76F71}">
   <dimension ref="A1:H105"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1796875" customWidth="1"/>
+    <col min="4" max="4" width="34.54296875" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -953,7 +1010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -979,7 +1036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1005,7 +1062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1031,7 +1088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1057,7 +1114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1083,7 +1140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1109,7 +1166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1135,7 +1192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1161,7 +1218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1187,7 +1244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1213,7 +1270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1239,7 +1296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1265,7 +1322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1291,7 +1348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1317,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1343,7 +1400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1369,7 +1426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1395,7 +1452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1421,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1447,7 +1504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1473,7 +1530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1499,7 +1556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1525,7 +1582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1551,7 +1608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1577,7 +1634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1603,7 +1660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1629,7 +1686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1655,7 +1712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1681,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1707,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1733,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1759,7 +1816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1785,7 +1842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1811,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1837,7 +1894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1863,7 +1920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1889,7 +1946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1915,7 +1972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1941,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1967,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1993,7 +2050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2019,7 +2076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2045,7 +2102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2071,7 +2128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2097,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2123,7 +2180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2149,7 +2206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2175,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2201,7 +2258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2227,7 +2284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2253,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2279,7 +2336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2305,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2331,7 +2388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2357,7 +2414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2383,7 +2440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2409,7 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2435,7 +2492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2461,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2487,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2513,7 +2570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2539,7 +2596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2565,7 +2622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -2591,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2617,7 +2674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -2643,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2669,7 +2726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -2695,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2721,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2747,7 +2804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2773,7 +2830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2799,7 +2856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2825,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2851,7 +2908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2877,7 +2934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2903,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -2929,11 +2986,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="C78" s="2" t="s">
         <v>23</v>
       </c>
@@ -2953,11 +3012,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="2">
         <v>78</v>
       </c>
-      <c r="B79" s="2"/>
+      <c r="B79" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="C79" s="2" t="s">
         <v>7</v>
       </c>
@@ -2977,11 +3038,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="2">
         <v>79</v>
       </c>
-      <c r="B80" s="2"/>
+      <c r="B80" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="C80" s="2" t="s">
         <v>11</v>
       </c>
@@ -3001,11 +3064,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="2">
         <v>80</v>
       </c>
-      <c r="B81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>150</v>
+      </c>
       <c r="C81" s="2" t="s">
         <v>45</v>
       </c>
@@ -3025,11 +3090,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" s="2"/>
+      <c r="B82" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="C82" s="2" t="s">
         <v>34</v>
       </c>
@@ -3049,11 +3116,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="2">
         <v>82</v>
       </c>
-      <c r="B83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="C83" s="2" t="s">
         <v>114</v>
       </c>
@@ -3073,11 +3142,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" s="2"/>
+      <c r="B84" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="C84" s="2" t="s">
         <v>4</v>
       </c>
@@ -3097,17 +3168,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="2">
         <v>84</v>
       </c>
-      <c r="B85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="C85" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="E85" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="F85" s="2" t="b">
         <v>0</v>
       </c>
@@ -3118,17 +3194,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="C86" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="E86" s="7" t="s">
+        <v>113</v>
+      </c>
       <c r="F86" s="2" t="b">
         <v>0</v>
       </c>
@@ -3139,17 +3220,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="2">
         <v>86</v>
       </c>
-      <c r="B87" s="2"/>
+      <c r="B87" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="C87" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E87" s="7" t="s">
+        <v>157</v>
+      </c>
       <c r="F87" s="2" t="b">
         <v>0</v>
       </c>
@@ -3160,17 +3246,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="2">
         <v>87</v>
       </c>
-      <c r="B88" s="2"/>
+      <c r="B88" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="C88" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="E88" s="7" t="s">
+        <v>134</v>
+      </c>
       <c r="F88" s="2" t="b">
         <v>0</v>
       </c>
@@ -3181,17 +3272,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="2">
         <v>88</v>
       </c>
-      <c r="B89" s="2"/>
+      <c r="B89" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="C89" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="E89" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="F89" s="2" t="b">
         <v>0</v>
       </c>
@@ -3202,13 +3298,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="2">
         <v>89</v>
       </c>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
+      <c r="B90" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>137</v>
+      </c>
       <c r="F90" s="2" t="b">
         <v>0</v>
       </c>
@@ -3219,11 +3324,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="2">
         <v>90</v>
       </c>
-      <c r="B91" s="3"/>
+      <c r="B91" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C91" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="F91" s="2" t="b">
         <v>0</v>
       </c>
@@ -3234,11 +3350,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="B92" s="3"/>
+      <c r="B92" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" t="s">
+        <v>38</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>135</v>
+      </c>
       <c r="F92" s="2" t="b">
         <v>0</v>
       </c>
@@ -3249,11 +3376,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="2">
         <v>92</v>
       </c>
-      <c r="B93" s="3"/>
+      <c r="B93" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C93" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" t="s">
+        <v>45</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>146</v>
+      </c>
       <c r="F93" s="2" t="b">
         <v>0</v>
       </c>
@@ -3264,11 +3402,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="2">
         <v>93</v>
       </c>
-      <c r="B94" s="3"/>
+      <c r="B94" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C94" t="s">
+        <v>47</v>
+      </c>
+      <c r="D94" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="F94" s="2" t="b">
         <v>0</v>
       </c>
@@ -3279,11 +3428,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="2">
         <v>94</v>
       </c>
-      <c r="B95" s="3"/>
+      <c r="B95" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C95" t="s">
+        <v>114</v>
+      </c>
+      <c r="D95" t="s">
+        <v>34</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>127</v>
+      </c>
       <c r="F95" s="2" t="b">
         <v>0</v>
       </c>
@@ -3294,11 +3454,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="2">
         <v>95</v>
       </c>
-      <c r="B96" s="3"/>
+      <c r="B96" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C96" t="s">
+        <v>39</v>
+      </c>
+      <c r="D96" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>134</v>
+      </c>
       <c r="F96" s="2" t="b">
         <v>0</v>
       </c>
@@ -3309,11 +3480,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="2">
         <v>96</v>
       </c>
-      <c r="B97" s="3"/>
+      <c r="B97" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C97" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97" t="s">
+        <v>50</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="F97" s="2" t="b">
         <v>0</v>
       </c>
@@ -3324,11 +3506,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="2">
         <v>97</v>
       </c>
-      <c r="B98" s="3"/>
+      <c r="B98" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C98" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" t="s">
+        <v>20</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>113</v>
+      </c>
       <c r="F98" s="2" t="b">
         <v>0</v>
       </c>
@@ -3339,11 +3532,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="2">
         <v>98</v>
       </c>
-      <c r="B99" s="3"/>
+      <c r="B99" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C99" t="s">
+        <v>4</v>
+      </c>
+      <c r="D99" t="s">
+        <v>34</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="F99" s="2" t="b">
         <v>0</v>
       </c>
@@ -3354,11 +3558,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="2">
         <v>99</v>
       </c>
-      <c r="B100" s="3"/>
+      <c r="B100" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C100" t="s">
+        <v>38</v>
+      </c>
+      <c r="D100" t="s">
+        <v>45</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>135</v>
+      </c>
       <c r="F100" s="2" t="b">
         <v>0</v>
       </c>
@@ -3369,11 +3584,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="2">
         <v>100</v>
       </c>
-      <c r="B101" s="3"/>
+      <c r="B101" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C101" t="s">
+        <v>39</v>
+      </c>
+      <c r="D101" t="s">
+        <v>22</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>126</v>
+      </c>
       <c r="F101" s="2" t="b">
         <v>0</v>
       </c>
@@ -3384,11 +3610,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="2">
         <v>101</v>
       </c>
-      <c r="B102" s="3"/>
+      <c r="B102" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C102" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" t="s">
+        <v>4</v>
+      </c>
       <c r="F102" s="2" t="b">
         <v>0</v>
       </c>
@@ -3399,11 +3633,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="2">
         <v>102</v>
       </c>
-      <c r="B103" s="3"/>
+      <c r="B103" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C103" t="s">
+        <v>45</v>
+      </c>
+      <c r="D103" t="s">
+        <v>39</v>
+      </c>
       <c r="F103" s="2" t="b">
         <v>0</v>
       </c>
@@ -3414,7 +3656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -3429,7 +3671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="2">
         <v>104</v>
       </c>

--- a/src/results.xlsx
+++ b/src/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029D1F33-3A01-47F6-9935-F4BAF765E892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795D6235-D154-4459-8E1D-8A26C784E4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1850" yWindow="16090" windowWidth="22780" windowHeight="14540" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{6C21F51B-054C-4E20-95EC-246A1F00C097}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="168">
   <si>
     <t>Match_ID</t>
   </si>
@@ -537,6 +537,12 @@
   </si>
   <si>
     <t>16 July 7:00am</t>
+  </si>
+  <si>
+    <t>19 July 9:00am</t>
+  </si>
+  <si>
+    <t>20 July 7:00am</t>
   </si>
 </sst>
 </file>
@@ -3623,6 +3629,9 @@
       <c r="D102" t="s">
         <v>4</v>
       </c>
+      <c r="E102" s="7" t="s">
+        <v>138</v>
+      </c>
       <c r="F102" s="2" t="b">
         <v>0</v>
       </c>
@@ -3646,6 +3655,9 @@
       <c r="D103" t="s">
         <v>39</v>
       </c>
+      <c r="E103" s="7" t="s">
+        <v>135</v>
+      </c>
       <c r="F103" s="2" t="b">
         <v>0</v>
       </c>
@@ -3660,7 +3672,15 @@
       <c r="A104" s="2">
         <v>103</v>
       </c>
-      <c r="B104" s="3"/>
+      <c r="B104" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C104" t="s">
+        <v>45</v>
+      </c>
+      <c r="D104" t="s">
+        <v>7</v>
+      </c>
       <c r="F104" s="2" t="b">
         <v>0</v>
       </c>
@@ -3675,7 +3695,15 @@
       <c r="A105" s="2">
         <v>104</v>
       </c>
-      <c r="B105" s="3"/>
+      <c r="B105" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C105" t="s">
+        <v>4</v>
+      </c>
+      <c r="D105" t="s">
+        <v>39</v>
+      </c>
       <c r="F105" s="2" t="b">
         <v>1</v>
       </c>
